--- a/top_20_antihypertensive.xlsx
+++ b/top_20_antihypertensive.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ammar/Desktop/Python example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E23F0C1-A699-794C-BCF5-F60441C57BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FFDBB15-FFDB-D24F-B06E-663C9ED79D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" xr2:uid="{17780EA3-C328-8D46-B401-09DCD116F5EC}"/>
+    <workbookView xWindow="34200" yWindow="620" windowWidth="51200" windowHeight="28180" xr2:uid="{17780EA3-C328-8D46-B401-09DCD116F5EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="180">
   <si>
     <t>Drug</t>
   </si>
@@ -549,13 +549,61 @@
   </si>
   <si>
     <t>Angiotensin Converting Enzyme Inhibitor</t>
+  </si>
+  <si>
+    <t>R
+(Accum.
+Factor)</t>
+  </si>
+  <si>
+    <t>SINGLE DOSE
+Cmax
+(ng/mL)</t>
+  </si>
+  <si>
+    <t>SINGLE DOSE
+Cmin
+(ng/mL)</t>
+  </si>
+  <si>
+    <t>Css,max
+(ng/mL)</t>
+  </si>
+  <si>
+    <t>Css,min
+(ng/mL)</t>
+  </si>
+  <si>
+    <t>Css,avg
+(ng/mL)</t>
+  </si>
+  <si>
+    <t>LOD
+(ng/mL)</t>
+  </si>
+  <si>
+    <t>Det.
+Window
+(h)</t>
+  </si>
+  <si>
+    <t>Det.
+Window
+(days)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -569,15 +617,20 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -585,26 +638,54 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="1" builtinId="10"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -936,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CBE478A-8802-9747-8B00-3BE777E7AE5C}">
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:T44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -951,9 +1032,11 @@
     <col min="10" max="10" width="18.33203125" customWidth="1"/>
     <col min="11" max="11" width="23.1640625" customWidth="1"/>
     <col min="12" max="12" width="17.33203125" customWidth="1"/>
+    <col min="13" max="13" width="23.1640625" customWidth="1"/>
+    <col min="14" max="14" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" s="1" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -987,1265 +1070,1363 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="2"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="L1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="2">
         <v>5</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="2">
         <v>4.41</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="2">
         <v>4</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="1"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="H2" s="2">
+        <v>64</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2">
+        <v>2.94</v>
+      </c>
+      <c r="M2" s="5">
+        <v>8.9</v>
+      </c>
+      <c r="N2" s="5">
+        <v>4.41</v>
+      </c>
+      <c r="O2" s="5">
+        <v>26.2</v>
+      </c>
+      <c r="P2" s="5">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>5.2</v>
+      </c>
+      <c r="R2" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="S2" s="7">
+        <v>201.67</v>
+      </c>
+      <c r="T2" s="8">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="2">
         <v>10</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="2">
         <v>6.13</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="2">
         <v>4</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="5">
+      <c r="G4" s="2"/>
+      <c r="H4" s="4">
         <v>1</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="1"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2">
+        <v>1.89</v>
+      </c>
+      <c r="M4" s="5">
+        <v>29.3</v>
+      </c>
+      <c r="N4" s="5">
+        <v>14.8</v>
+      </c>
+      <c r="O4" s="5">
+        <v>55.2</v>
+      </c>
+      <c r="P4" s="5">
+        <v>28.03</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>44.7</v>
+      </c>
+      <c r="R4" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="S4" s="7">
+        <v>134.41999999999999</v>
+      </c>
+      <c r="T4" s="8">
+        <f t="shared" ref="T4" si="0">S4/24</f>
+        <v>5.6008333333333331</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <v>8</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="2">
         <v>29.67</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>1</v>
       </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="1"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="2">
         <v>2</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="2">
         <v>5.77</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="2">
         <v>12.3</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4" t="s">
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4" t="s">
+      <c r="J6" s="2"/>
+      <c r="K6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="L6" s="1"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <v>10</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="2">
         <v>1.66</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="1"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2">
+        <v>1.49</v>
+      </c>
+      <c r="M7" s="5">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1.66</v>
+      </c>
+      <c r="O7" s="5">
+        <v>25.92</v>
+      </c>
+      <c r="P7" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>25.8</v>
+      </c>
+      <c r="R7" s="6">
+        <v>2.25</v>
+      </c>
+      <c r="S7" s="7">
+        <v>52.9</v>
+      </c>
+      <c r="T7" s="8">
+        <f t="shared" ref="T7" si="1">S7/24</f>
+        <v>2.2041666666666666</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="2">
         <v>2.5</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4" t="s">
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4" t="s">
+      <c r="G8" s="2"/>
+      <c r="H8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="2">
         <v>36</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="1"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="2">
         <v>5</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4" t="s">
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4" t="s">
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="1"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="2">
         <v>2.5</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4" t="s">
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4" t="s">
+      <c r="G10" s="2"/>
+      <c r="H10" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="2">
         <v>36</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="1"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="2">
         <v>10</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="2">
         <v>7.54</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="2">
         <v>51</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="2">
         <v>1.5</v>
       </c>
-      <c r="G11" s="4">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4">
+      <c r="G11" s="2">
+        <v>11</v>
+      </c>
+      <c r="H11" s="2">
+        <v>90</v>
+      </c>
+      <c r="I11" s="2">
         <v>244</v>
       </c>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4">
-        <v>197</v>
-      </c>
-      <c r="L11" s="1"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="J11" s="2"/>
+      <c r="K11" s="2">
+        <v>242</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1.28</v>
+      </c>
+      <c r="M11" s="5">
+        <v>51</v>
+      </c>
+      <c r="N11" s="5">
+        <v>7.54</v>
+      </c>
+      <c r="O11" s="5">
+        <v>65.400000000000006</v>
+      </c>
+      <c r="P11" s="5">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>24.6</v>
+      </c>
+      <c r="R11" s="6">
+        <v>2.42</v>
+      </c>
+      <c r="S11" s="7">
+        <v>52.33</v>
+      </c>
+      <c r="T11" s="8">
+        <f t="shared" ref="T11" si="2">S11/24</f>
+        <v>2.1804166666666664</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="2">
         <v>2.5</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="2">
         <v>0</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4" t="s">
+      <c r="F12" s="2"/>
+      <c r="G12" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>0.9</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4" t="s">
+      <c r="J12" s="2"/>
+      <c r="K12" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="L12" s="1"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="2">
         <v>25</v>
       </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="1"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>168</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="2">
         <v>50</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="2">
         <v>0.01</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4" t="s">
+      <c r="H14" s="2"/>
+      <c r="I14" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="1"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>168</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="2">
         <v>25</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="2">
         <v>0.1</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4" t="s">
+      <c r="H15" s="2"/>
+      <c r="I15" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="1"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>168</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="2">
         <v>100</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="2">
         <v>0.01</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4" t="s">
+      <c r="H16" s="2"/>
+      <c r="I16" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="1"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="2">
         <v>2.5</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="2">
         <v>1.18</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="2">
         <v>23</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="2">
         <v>2</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="2">
         <v>5.6</v>
       </c>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4" t="s">
+      <c r="H17" s="2"/>
+      <c r="I17" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K17" s="4">
+      <c r="K17" s="2">
         <v>1</v>
       </c>
-      <c r="L17" s="1"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="2">
         <v>5</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="2">
         <v>0.86</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4" t="s">
+      <c r="H18" s="2"/>
+      <c r="I18" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="J18" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="K18" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="L18" s="1"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="2">
         <v>20</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="2">
         <v>0.09</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="I19" s="4"/>
-      <c r="J19" s="5">
+      <c r="I19" s="2"/>
+      <c r="J19" s="4">
         <v>0.37</v>
       </c>
-      <c r="K19" s="4"/>
-      <c r="L19" s="1"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K19" s="2"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="2">
         <v>80</v>
       </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4">
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2">
         <v>0.9</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4" t="s">
+      <c r="J20" s="2"/>
+      <c r="K20" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="L20" s="1"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="2">
         <v>8</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="2">
         <v>8.1199999999999992</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="1"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="2">
         <v>2</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="2">
         <v>1.97</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="1"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="2">
         <v>4</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="2">
         <v>4.6399999999999997</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="1"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="2">
         <v>12</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="2">
         <v>16.72</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="1"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="2">
         <v>16</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="2">
         <v>19.16</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="1"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="2">
         <v>25</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="2">
         <v>1.3</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4" t="s">
+      <c r="H26" s="2"/>
+      <c r="I26" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="1"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="2">
         <v>50</v>
       </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4" t="s">
+      <c r="D27" s="2"/>
+      <c r="E27" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="1"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="2">
         <v>100</v>
       </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4" t="s">
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4">
+      <c r="H28" s="2"/>
+      <c r="I28" s="2">
         <v>112.5</v>
       </c>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4" t="s">
+      <c r="J28" s="2"/>
+      <c r="K28" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="L28" s="1"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="2">
         <v>10</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="2">
         <v>18.010000000000002</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4" t="s">
+      <c r="H29" s="2"/>
+      <c r="I29" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="J29" s="4" t="s">
+      <c r="J29" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="K29" s="4"/>
-      <c r="L29" s="1"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K29" s="2"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="2">
         <v>150</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="2">
         <v>671.75</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="2">
         <v>1.5</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4" t="s">
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="K30" s="4"/>
-      <c r="L30" s="1"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K30" s="2"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="2">
         <v>300</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="2">
         <v>883.78</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="2">
         <v>1.5</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4" t="s">
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="K31" s="4"/>
-      <c r="L31" s="1"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K31" s="2"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="2">
         <v>300</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="2">
         <v>1262.21</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="2">
         <v>1</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4" t="s">
+      <c r="H32" s="2"/>
+      <c r="I32" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="J32" s="4" t="s">
+      <c r="J32" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="K32" s="4"/>
-      <c r="L32" s="1"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K32" s="2"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="2">
         <v>60</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="2">
         <v>0.92</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="1"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="2">
         <v>120</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="2">
         <v>0</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4" t="s">
+      <c r="F34" s="2"/>
+      <c r="G34" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="I34" s="4" t="s">
+      <c r="I34" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4" t="s">
+      <c r="J34" s="2"/>
+      <c r="K34" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="L34" s="1"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="2">
         <v>0.3</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="2">
         <v>0</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4" t="s">
+      <c r="H35" s="2"/>
+      <c r="I35" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4" t="s">
+      <c r="J35" s="2"/>
+      <c r="K35" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="L35" s="1"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="2">
         <v>4</v>
       </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4">
+      <c r="D36" s="2"/>
+      <c r="E36" s="2">
         <v>5.5</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="2">
         <v>4</v>
       </c>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4" t="s">
+      <c r="G36" s="2"/>
+      <c r="H36" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4" t="s">
+      <c r="I36" s="2"/>
+      <c r="J36" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="K36" s="4"/>
-      <c r="L36" s="1"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K36" s="2"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="2">
         <v>8</v>
       </c>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4" t="s">
+      <c r="D37" s="2"/>
+      <c r="E37" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4" t="s">
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="1"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="2">
         <v>80</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="2">
         <v>114.95</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F38" s="2">
         <v>3</v>
       </c>
-      <c r="G38" s="4">
+      <c r="G38" s="2">
         <v>5.0999999999999996</v>
       </c>
-      <c r="H38" s="5">
+      <c r="H38" s="4">
         <v>0.25</v>
       </c>
-      <c r="I38" s="4">
+      <c r="I38" s="2">
         <v>132</v>
       </c>
-      <c r="J38" s="5">
+      <c r="J38" s="4">
         <v>0.1</v>
       </c>
-      <c r="K38" s="4">
+      <c r="K38" s="2">
         <v>9.5</v>
       </c>
-      <c r="L38" s="1"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="2">
         <v>25</v>
       </c>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4" t="s">
+      <c r="D39" s="2"/>
+      <c r="E39" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="2">
         <v>1.5</v>
       </c>
-      <c r="G39" s="4"/>
-      <c r="H39" s="5">
+      <c r="G39" s="2"/>
+      <c r="H39" s="4">
         <v>0.72</v>
       </c>
-      <c r="I39" s="4" t="s">
+      <c r="I39" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="1"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="2">
         <v>12.5</v>
       </c>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4" t="s">
+      <c r="D40" s="2"/>
+      <c r="E40" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="2">
         <v>1.5</v>
       </c>
-      <c r="G40" s="4"/>
-      <c r="H40" s="5">
+      <c r="G40" s="2"/>
+      <c r="H40" s="4">
         <v>0.68</v>
       </c>
-      <c r="I40" s="4" t="s">
+      <c r="I40" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="1"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="2">
         <v>50</v>
       </c>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4" t="s">
+      <c r="D41" s="2"/>
+      <c r="E41" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F41" s="2">
         <v>1.5</v>
       </c>
-      <c r="G41" s="4"/>
-      <c r="H41" s="5">
+      <c r="G41" s="2"/>
+      <c r="H41" s="4">
         <v>0.65</v>
       </c>
-      <c r="I41" s="4" t="s">
+      <c r="I41" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="1"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="2">
         <v>80</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="2">
         <v>247.01</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F42" s="2">
         <v>1</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4" t="s">
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="K42" s="4"/>
-      <c r="L42" s="1"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K42" s="2"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="2">
         <v>20</v>
       </c>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4" t="s">
+      <c r="D43" s="2"/>
+      <c r="E43" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F43" s="2">
         <v>4</v>
       </c>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4" t="s">
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="K43" s="4"/>
-      <c r="L43" s="1"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K43" s="2"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>167</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="2">
         <v>10</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="2">
         <v>0.09</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4" t="s">
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K44" s="4"/>
-      <c r="L44" s="1"/>
+      <c r="K44" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/top_20_antihypertensive.xlsx
+++ b/top_20_antihypertensive.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ammar/Desktop/Python example/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniofleicester-my.sharepoint.com/personal/maa117_leicester_ac_uk/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FFDBB15-FFDB-D24F-B06E-663C9ED79D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{7562AD40-5584-2B4C-BB93-5D06383FE9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51F6B6FA-FF80-A844-8252-358897CF62CA}"/>
   <bookViews>
-    <workbookView xWindow="34200" yWindow="620" windowWidth="51200" windowHeight="28180" xr2:uid="{17780EA3-C328-8D46-B401-09DCD116F5EC}"/>
+    <workbookView xWindow="0" yWindow="700" windowWidth="34200" windowHeight="19960" xr2:uid="{17780EA3-C328-8D46-B401-09DCD116F5EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -596,7 +596,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -616,8 +616,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -627,6 +632,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFA500"/>
+        <bgColor rgb="FFFFA500"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor rgb="FF00B050"/>
       </patternFill>
     </fill>
   </fills>
@@ -658,7 +675,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -681,6 +698,15 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1123,9 +1149,15 @@
       <c r="H2" s="2">
         <v>64</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
+      <c r="I2" s="9">
+        <v>490</v>
+      </c>
+      <c r="J2" s="9">
+        <v>5</v>
+      </c>
+      <c r="K2" s="9">
+        <v>1470</v>
+      </c>
       <c r="L2" s="2">
         <v>2.94</v>
       </c>
@@ -1176,10 +1208,45 @@
       <c r="G3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
+      <c r="H3" s="9">
+        <v>64</v>
+      </c>
+      <c r="I3" s="9">
+        <v>490</v>
+      </c>
+      <c r="J3" s="9">
+        <v>5</v>
+      </c>
+      <c r="K3" s="9">
+        <v>1470</v>
+      </c>
+      <c r="L3" s="10">
+        <v>4.1070000000000002</v>
+      </c>
+      <c r="M3" s="10">
+        <v>8.1</v>
+      </c>
+      <c r="N3" s="10">
+        <v>6.13</v>
+      </c>
+      <c r="O3" s="10">
+        <v>33.264000000000003</v>
+      </c>
+      <c r="P3" s="10">
+        <v>25.1739</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>9.07</v>
+      </c>
+      <c r="R3" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="S3" s="10">
+        <v>320.58600000000001</v>
+      </c>
+      <c r="T3" s="10">
+        <v>13.357751</v>
+      </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
@@ -1191,20 +1258,30 @@
       <c r="C4" s="2">
         <v>4</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="10">
+        <v>15.4582</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>38</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="2"/>
+      <c r="G4" s="9">
+        <v>22</v>
+      </c>
       <c r="H4" s="4">
         <v>1</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
+      <c r="I4" s="9">
+        <v>105</v>
+      </c>
+      <c r="J4" s="9">
+        <v>5</v>
+      </c>
+      <c r="K4" s="9">
+        <v>105</v>
+      </c>
       <c r="L4" s="2">
         <v>1.89</v>
       </c>
@@ -1230,8 +1307,7 @@
         <v>134.41999999999999</v>
       </c>
       <c r="T4" s="8">
-        <f t="shared" ref="T4" si="0">S4/24</f>
-        <v>5.6008333333333331</v>
+        <v>5.6008329999999997</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
@@ -1259,9 +1335,42 @@
       <c r="H5" s="4">
         <v>1</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+      <c r="I5" s="9">
+        <v>105</v>
+      </c>
+      <c r="J5" s="9">
+        <v>5</v>
+      </c>
+      <c r="K5" s="9">
+        <v>105</v>
+      </c>
+      <c r="L5" s="10">
+        <v>1.7989999999999999</v>
+      </c>
+      <c r="M5" s="10">
+        <v>66.8</v>
+      </c>
+      <c r="N5" s="10">
+        <v>29.67</v>
+      </c>
+      <c r="O5" s="10">
+        <v>120.203</v>
+      </c>
+      <c r="P5" s="10">
+        <v>53.389499999999998</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>52.91</v>
+      </c>
+      <c r="R5" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="S5" s="10">
+        <v>148.27199999999999</v>
+      </c>
+      <c r="T5" s="10">
+        <v>6.1780109999999997</v>
+      </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
@@ -1285,13 +1394,44 @@
       <c r="G6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="2"/>
+      <c r="H6" s="9">
+        <v>65</v>
+      </c>
       <c r="I6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J6" s="2"/>
+      <c r="J6" s="9">
+        <v>5</v>
+      </c>
       <c r="K6" s="2" t="s">
         <v>46</v>
+      </c>
+      <c r="L6" s="10">
+        <v>1.885</v>
+      </c>
+      <c r="M6" s="10">
+        <v>12.3</v>
+      </c>
+      <c r="N6" s="10">
+        <v>5.77</v>
+      </c>
+      <c r="O6" s="10">
+        <v>23.187000000000001</v>
+      </c>
+      <c r="P6" s="10">
+        <v>10.8774</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>4.2190000000000003</v>
+      </c>
+      <c r="R6" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="S6" s="10">
+        <v>106.88</v>
+      </c>
+      <c r="T6" s="10">
+        <v>4.453354</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.2">
@@ -1316,9 +1456,13 @@
       <c r="G7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="2"/>
+      <c r="H7" s="9">
+        <v>28</v>
+      </c>
       <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+      <c r="J7" s="9">
+        <v>23</v>
+      </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2">
         <v>1.49</v>
@@ -1345,8 +1489,7 @@
         <v>52.9</v>
       </c>
       <c r="T7" s="8">
-        <f t="shared" ref="T7" si="1">S7/24</f>
-        <v>2.2041666666666666</v>
+        <v>2.204167</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
@@ -1377,6 +1520,9 @@
         <v>54</v>
       </c>
       <c r="K8" s="2"/>
+      <c r="R8" s="9">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
@@ -1388,14 +1534,18 @@
       <c r="C9" s="2">
         <v>5</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" s="10">
+        <v>8.3999999999999995E-3</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="2"/>
+      <c r="G9" s="9">
+        <v>2</v>
+      </c>
       <c r="H9" s="2" t="s">
         <v>57</v>
       </c>
@@ -1406,6 +1556,33 @@
         <v>59</v>
       </c>
       <c r="K9" s="2"/>
+      <c r="L9" s="10">
+        <v>1</v>
+      </c>
+      <c r="M9" s="10">
+        <v>21.1</v>
+      </c>
+      <c r="N9" s="10">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="O9" s="10">
+        <v>21.105</v>
+      </c>
+      <c r="P9" s="10">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>10.510999999999999</v>
+      </c>
+      <c r="R9" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="S9" s="10">
+        <v>6.4610000000000003</v>
+      </c>
+      <c r="T9" s="10">
+        <v>0.26918900000000001</v>
+      </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -1417,14 +1594,18 @@
       <c r="C10" s="2">
         <v>2.5</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="10">
+        <v>0.85819999999999996</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>60</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="2"/>
+      <c r="G10" s="9">
+        <v>13</v>
+      </c>
       <c r="H10" s="2" t="s">
         <v>62</v>
       </c>
@@ -1434,7 +1615,36 @@
       <c r="J10" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="2"/>
+      <c r="K10" s="10">
+        <v>40.5</v>
+      </c>
+      <c r="L10" s="10">
+        <v>1.385</v>
+      </c>
+      <c r="M10" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="N10" s="10">
+        <v>0.85819999999999996</v>
+      </c>
+      <c r="O10" s="10">
+        <v>3.7410000000000001</v>
+      </c>
+      <c r="P10" s="10">
+        <v>1.1891</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>13.503</v>
+      </c>
+      <c r="R10" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="S10" s="10">
+        <v>9.5380000000000003</v>
+      </c>
+      <c r="T10" s="10">
+        <v>0.39739600000000003</v>
+      </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
@@ -1464,7 +1674,9 @@
       <c r="I11" s="2">
         <v>244</v>
       </c>
-      <c r="J11" s="2"/>
+      <c r="J11" s="9">
+        <v>50</v>
+      </c>
       <c r="K11" s="2">
         <v>242</v>
       </c>
@@ -1493,8 +1705,7 @@
         <v>52.33</v>
       </c>
       <c r="T11" s="8">
-        <f t="shared" ref="T11" si="2">S11/24</f>
-        <v>2.1804166666666664</v>
+        <v>2.1804169999999998</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
@@ -1513,7 +1724,9 @@
       <c r="E12" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F12" s="2"/>
+      <c r="F12" s="9">
+        <v>1.5</v>
+      </c>
       <c r="G12" s="2" t="s">
         <v>67</v>
       </c>
@@ -1523,9 +1736,38 @@
       <c r="I12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="J12" s="2"/>
+      <c r="J12" s="9">
+        <v>7</v>
+      </c>
       <c r="K12" s="2" t="s">
         <v>69</v>
+      </c>
+      <c r="L12" s="10">
+        <v>1</v>
+      </c>
+      <c r="M12" s="10">
+        <v>154</v>
+      </c>
+      <c r="N12" s="10">
+        <v>0</v>
+      </c>
+      <c r="O12" s="10">
+        <v>154</v>
+      </c>
+      <c r="P12" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>744.048</v>
+      </c>
+      <c r="R12" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="S12" s="10">
+        <v>6.6150000000000002</v>
+      </c>
+      <c r="T12" s="10">
+        <v>0.27561799999999997</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.2">
@@ -1538,14 +1780,57 @@
       <c r="C13" s="2">
         <v>25</v>
       </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
+      <c r="D13" s="10">
+        <v>24.7332</v>
+      </c>
+      <c r="E13" s="9">
+        <v>60</v>
+      </c>
+      <c r="F13" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G13" s="9">
+        <v>16.5</v>
+      </c>
+      <c r="H13" s="9">
+        <v>73</v>
+      </c>
+      <c r="I13" s="9">
+        <v>294</v>
+      </c>
+      <c r="J13" s="9">
+        <v>2</v>
+      </c>
+      <c r="K13" s="10">
+        <v>420</v>
+      </c>
+      <c r="L13" s="10">
+        <v>1.575</v>
+      </c>
+      <c r="M13" s="10">
+        <v>60</v>
+      </c>
+      <c r="N13" s="10">
+        <v>24.7332</v>
+      </c>
+      <c r="O13" s="10">
+        <v>94.48</v>
+      </c>
+      <c r="P13" s="10">
+        <v>38.9467</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>43.107999999999997</v>
+      </c>
+      <c r="R13" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="S13" s="10">
+        <v>113.608</v>
+      </c>
+      <c r="T13" s="10">
+        <v>4.7336619999999998</v>
+      </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
@@ -1569,12 +1854,45 @@
       <c r="G14" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H14" s="2"/>
+      <c r="H14" s="9">
+        <v>33</v>
+      </c>
       <c r="I14" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
+      <c r="J14" s="9">
+        <v>4</v>
+      </c>
+      <c r="K14" s="9">
+        <v>34</v>
+      </c>
+      <c r="L14" s="10">
+        <v>1</v>
+      </c>
+      <c r="M14" s="10">
+        <v>197.6</v>
+      </c>
+      <c r="N14" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="O14" s="10">
+        <v>197.61099999999999</v>
+      </c>
+      <c r="P14" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>122.812</v>
+      </c>
+      <c r="R14" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="S14" s="10">
+        <v>13.436</v>
+      </c>
+      <c r="T14" s="10">
+        <v>0.55982200000000004</v>
+      </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
@@ -1598,12 +1916,45 @@
       <c r="G15" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H15" s="2"/>
+      <c r="H15" s="9">
+        <v>33</v>
+      </c>
       <c r="I15" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
+      <c r="J15" s="9">
+        <v>4</v>
+      </c>
+      <c r="K15" s="9">
+        <v>34</v>
+      </c>
+      <c r="L15" s="10">
+        <v>1.0009999999999999</v>
+      </c>
+      <c r="M15" s="10">
+        <v>84.5</v>
+      </c>
+      <c r="N15" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="O15" s="10">
+        <v>84.602999999999994</v>
+      </c>
+      <c r="P15" s="10">
+        <v>0.10009999999999999</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>52.901000000000003</v>
+      </c>
+      <c r="R15" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="S15" s="10">
+        <v>16.68</v>
+      </c>
+      <c r="T15" s="10">
+        <v>0.69501900000000005</v>
+      </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
@@ -1627,14 +1978,47 @@
       <c r="G16" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="H16" s="2"/>
+      <c r="H16" s="9">
+        <v>33</v>
+      </c>
       <c r="I16" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J16" s="9">
+        <v>4</v>
+      </c>
+      <c r="K16" s="9">
+        <v>34</v>
+      </c>
+      <c r="L16" s="10">
+        <v>1</v>
+      </c>
+      <c r="M16" s="10">
+        <v>800.5</v>
+      </c>
+      <c r="N16" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="O16" s="10">
+        <v>800.51300000000003</v>
+      </c>
+      <c r="P16" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>335.53</v>
+      </c>
+      <c r="R16" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="S16" s="10">
+        <v>15.053000000000001</v>
+      </c>
+      <c r="T16" s="10">
+        <v>0.62720500000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>18</v>
       </c>
@@ -1656,7 +2040,9 @@
       <c r="G17" s="2">
         <v>5.6</v>
       </c>
-      <c r="H17" s="2"/>
+      <c r="H17" s="9">
+        <v>100</v>
+      </c>
       <c r="I17" s="2" t="s">
         <v>83</v>
       </c>
@@ -1666,8 +2052,35 @@
       <c r="K17" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="10">
+        <v>1.054</v>
+      </c>
+      <c r="M17" s="10">
+        <v>23</v>
+      </c>
+      <c r="N17" s="10">
+        <v>1.18</v>
+      </c>
+      <c r="O17" s="10">
+        <v>24.244</v>
+      </c>
+      <c r="P17" s="10">
+        <v>1.2438</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>18.667999999999999</v>
+      </c>
+      <c r="R17" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="S17" s="10">
+        <v>27.565999999999999</v>
+      </c>
+      <c r="T17" s="10">
+        <v>1.14859</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
@@ -1689,7 +2102,9 @@
       <c r="G18" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H18" s="2"/>
+      <c r="H18" s="9">
+        <v>100</v>
+      </c>
       <c r="I18" s="2" t="s">
         <v>87</v>
       </c>
@@ -1699,8 +2114,35 @@
       <c r="K18" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="10">
+        <v>1.018</v>
+      </c>
+      <c r="M18" s="10">
+        <v>50</v>
+      </c>
+      <c r="N18" s="10">
+        <v>0.86</v>
+      </c>
+      <c r="O18" s="10">
+        <v>50.881</v>
+      </c>
+      <c r="P18" s="10">
+        <v>0.87509999999999999</v>
+      </c>
+      <c r="Q18" s="10">
+        <v>72.337999999999994</v>
+      </c>
+      <c r="R18" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="S18" s="10">
+        <v>24.568000000000001</v>
+      </c>
+      <c r="T18" s="10">
+        <v>1.0236769999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>19</v>
       </c>
@@ -1725,13 +2167,44 @@
       <c r="H19" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="I19" s="2"/>
+      <c r="I19" s="9">
+        <v>155</v>
+      </c>
       <c r="J19" s="4">
         <v>0.37</v>
       </c>
-      <c r="K19" s="2"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K19" s="10">
+        <v>25.5</v>
+      </c>
+      <c r="L19" s="10">
+        <v>1</v>
+      </c>
+      <c r="M19" s="10">
+        <v>552</v>
+      </c>
+      <c r="N19" s="10">
+        <v>0.09</v>
+      </c>
+      <c r="O19" s="10">
+        <v>552.08699999999999</v>
+      </c>
+      <c r="P19" s="10">
+        <v>0.09</v>
+      </c>
+      <c r="Q19" s="10">
+        <v>42.115000000000002</v>
+      </c>
+      <c r="R19" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="S19" s="10">
+        <v>17.922000000000001</v>
+      </c>
+      <c r="T19" s="10">
+        <v>0.74675400000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -1741,9 +2214,15 @@
       <c r="C20" s="2">
         <v>80</v>
       </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+      <c r="D20" s="10">
+        <v>1E-4</v>
+      </c>
+      <c r="E20" s="10">
+        <v>2208</v>
+      </c>
+      <c r="F20" s="10">
+        <v>1.5</v>
+      </c>
       <c r="G20" s="2">
         <v>0.9</v>
       </c>
@@ -1757,8 +2236,25 @@
       <c r="K20" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="10">
+        <v>1</v>
+      </c>
+      <c r="M20" s="10">
+        <v>2208</v>
+      </c>
+      <c r="N20" s="10">
+        <v>1E-4</v>
+      </c>
+      <c r="O20" s="11"/>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="S20" s="11"/>
+      <c r="T20" s="11"/>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
@@ -1780,12 +2276,47 @@
       <c r="G21" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H21" s="9">
+        <v>15</v>
+      </c>
+      <c r="I21" s="9">
+        <v>26</v>
+      </c>
+      <c r="J21" s="9">
+        <v>26</v>
+      </c>
+      <c r="K21" s="9">
+        <v>9.1</v>
+      </c>
+      <c r="L21" s="10">
+        <v>1.1919999999999999</v>
+      </c>
+      <c r="M21" s="10">
+        <v>50.5</v>
+      </c>
+      <c r="N21" s="10">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="O21" s="10">
+        <v>60.174999999999997</v>
+      </c>
+      <c r="P21" s="10">
+        <v>9.6757000000000009</v>
+      </c>
+      <c r="Q21" s="10">
+        <v>32.051000000000002</v>
+      </c>
+      <c r="R21" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="S21" s="10">
+        <v>56.732999999999997</v>
+      </c>
+      <c r="T21" s="10">
+        <v>2.3638560000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>20</v>
       </c>
@@ -1807,12 +2338,47 @@
       <c r="G22" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H22" s="9">
+        <v>15</v>
+      </c>
+      <c r="I22" s="9">
+        <v>26</v>
+      </c>
+      <c r="J22" s="9">
+        <v>26</v>
+      </c>
+      <c r="K22" s="9">
+        <v>9.1</v>
+      </c>
+      <c r="L22" s="10">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="M22" s="10">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="N22" s="10">
+        <v>1.97</v>
+      </c>
+      <c r="O22" s="10">
+        <v>19.329000000000001</v>
+      </c>
+      <c r="P22" s="10">
+        <v>2.2267999999999999</v>
+      </c>
+      <c r="Q22" s="10">
+        <v>8.0129999999999999</v>
+      </c>
+      <c r="R22" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="S22" s="10">
+        <v>35.386000000000003</v>
+      </c>
+      <c r="T22" s="10">
+        <v>1.474421</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>20</v>
       </c>
@@ -1834,12 +2400,47 @@
       <c r="G23" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H23" s="9">
+        <v>15</v>
+      </c>
+      <c r="I23" s="9">
+        <v>26</v>
+      </c>
+      <c r="J23" s="9">
+        <v>26</v>
+      </c>
+      <c r="K23" s="9">
+        <v>9.1</v>
+      </c>
+      <c r="L23" s="10">
+        <v>1.196</v>
+      </c>
+      <c r="M23" s="10">
+        <v>28.3</v>
+      </c>
+      <c r="N23" s="10">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="O23" s="10">
+        <v>33.851999999999997</v>
+      </c>
+      <c r="P23" s="10">
+        <v>5.5503</v>
+      </c>
+      <c r="Q23" s="10">
+        <v>16.026</v>
+      </c>
+      <c r="R23" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="S23" s="10">
+        <v>49.719000000000001</v>
+      </c>
+      <c r="T23" s="10">
+        <v>2.0716269999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>20</v>
       </c>
@@ -1861,12 +2462,47 @@
       <c r="G24" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H24" s="9">
+        <v>15</v>
+      </c>
+      <c r="I24" s="9">
+        <v>26</v>
+      </c>
+      <c r="J24" s="9">
+        <v>26</v>
+      </c>
+      <c r="K24" s="9">
+        <v>9.1</v>
+      </c>
+      <c r="L24" s="10">
+        <v>1.38</v>
+      </c>
+      <c r="M24" s="10">
+        <v>60.7</v>
+      </c>
+      <c r="N24" s="10">
+        <v>16.72</v>
+      </c>
+      <c r="O24" s="10">
+        <v>83.778000000000006</v>
+      </c>
+      <c r="P24" s="10">
+        <v>23.076799999999999</v>
+      </c>
+      <c r="Q24" s="10">
+        <v>48.076999999999998</v>
+      </c>
+      <c r="R24" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="S24" s="10">
+        <v>86.582999999999998</v>
+      </c>
+      <c r="T24" s="10">
+        <v>3.607621</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>20</v>
       </c>
@@ -1888,12 +2524,47 @@
       <c r="G25" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H25" s="9">
+        <v>15</v>
+      </c>
+      <c r="I25" s="9">
+        <v>26</v>
+      </c>
+      <c r="J25" s="9">
+        <v>26</v>
+      </c>
+      <c r="K25" s="9">
+        <v>9.1</v>
+      </c>
+      <c r="L25" s="10">
+        <v>1.1919999999999999</v>
+      </c>
+      <c r="M25" s="10">
+        <v>119.2</v>
+      </c>
+      <c r="N25" s="10">
+        <v>19.16</v>
+      </c>
+      <c r="O25" s="10">
+        <v>142.03700000000001</v>
+      </c>
+      <c r="P25" s="10">
+        <v>22.8308</v>
+      </c>
+      <c r="Q25" s="10">
+        <v>64.102999999999994</v>
+      </c>
+      <c r="R25" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="S25" s="10">
+        <v>68.010000000000005</v>
+      </c>
+      <c r="T25" s="10">
+        <v>2.8337539999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>21</v>
       </c>
@@ -1915,14 +2586,47 @@
       <c r="G26" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H26" s="2"/>
+      <c r="H26" s="9">
+        <v>52</v>
+      </c>
       <c r="I26" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J26" s="9">
+        <v>50</v>
+      </c>
+      <c r="K26" s="9">
+        <v>63</v>
+      </c>
+      <c r="L26" s="10">
+        <v>1.0109999999999999</v>
+      </c>
+      <c r="M26" s="10">
+        <v>117</v>
+      </c>
+      <c r="N26" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="O26" s="10">
+        <v>118.321</v>
+      </c>
+      <c r="P26" s="10">
+        <v>1.3147</v>
+      </c>
+      <c r="Q26" s="10">
+        <v>112.84699999999999</v>
+      </c>
+      <c r="R26" s="9">
+        <v>4.37</v>
+      </c>
+      <c r="S26" s="10">
+        <v>17.611999999999998</v>
+      </c>
+      <c r="T26" s="10">
+        <v>0.73382400000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>21</v>
       </c>
@@ -1932,18 +2636,59 @@
       <c r="C27" s="2">
         <v>50</v>
       </c>
-      <c r="D27" s="2"/>
+      <c r="D27" s="10">
+        <v>21.738199999999999</v>
+      </c>
       <c r="E27" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="F27" s="9">
+        <v>3</v>
+      </c>
+      <c r="G27" s="9">
+        <v>6.3</v>
+      </c>
+      <c r="H27" s="9">
+        <v>54</v>
+      </c>
+      <c r="I27" s="9">
+        <v>178</v>
+      </c>
+      <c r="J27" s="9">
+        <v>50</v>
+      </c>
+      <c r="K27" s="9">
+        <v>63</v>
+      </c>
+      <c r="L27" s="10">
+        <v>1.077</v>
+      </c>
+      <c r="M27" s="10">
+        <v>219</v>
+      </c>
+      <c r="N27" s="10">
+        <v>21.738199999999999</v>
+      </c>
+      <c r="O27" s="10">
+        <v>235.82900000000001</v>
+      </c>
+      <c r="P27" s="10">
+        <v>23.4087</v>
+      </c>
+      <c r="Q27" s="10">
+        <v>105.337</v>
+      </c>
+      <c r="R27" s="9">
+        <v>4.37</v>
+      </c>
+      <c r="S27" s="10">
+        <v>36.258000000000003</v>
+      </c>
+      <c r="T27" s="10">
+        <v>1.5107360000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>21</v>
       </c>
@@ -1953,22 +2698,59 @@
       <c r="C28" s="2">
         <v>100</v>
       </c>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
+      <c r="D28" s="10">
+        <v>28.497399999999999</v>
+      </c>
+      <c r="E28" s="10">
+        <v>468</v>
+      </c>
+      <c r="F28" s="9">
+        <v>3</v>
+      </c>
       <c r="G28" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="H28" s="2"/>
+      <c r="H28" s="9">
+        <v>58</v>
+      </c>
       <c r="I28" s="2">
         <v>112.5</v>
       </c>
-      <c r="J28" s="2"/>
+      <c r="J28" s="9">
+        <v>50</v>
+      </c>
       <c r="K28" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="10">
+        <v>1.0429999999999999</v>
+      </c>
+      <c r="M28" s="10">
+        <v>468</v>
+      </c>
+      <c r="N28" s="10">
+        <v>0</v>
+      </c>
+      <c r="O28" s="10">
+        <v>487.91899999999998</v>
+      </c>
+      <c r="P28" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="10">
+        <v>358.02499999999998</v>
+      </c>
+      <c r="R28" s="9">
+        <v>4.37</v>
+      </c>
+      <c r="S28" s="10">
+        <v>35.381999999999998</v>
+      </c>
+      <c r="T28" s="10">
+        <v>1.474267</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
@@ -1990,16 +2772,47 @@
       <c r="G29" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="H29" s="2"/>
+      <c r="H29" s="9">
+        <v>25</v>
+      </c>
       <c r="I29" s="2" t="s">
         <v>122</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="K29" s="2"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="9">
+        <v>124</v>
+      </c>
+      <c r="L29" s="10">
+        <v>1.794</v>
+      </c>
+      <c r="M29" s="10">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="N29" s="10">
+        <v>18.010000000000002</v>
+      </c>
+      <c r="O29" s="10">
+        <v>73.006</v>
+      </c>
+      <c r="P29" s="10">
+        <v>32.305500000000002</v>
+      </c>
+      <c r="Q29" s="10">
+        <v>17.934999999999999</v>
+      </c>
+      <c r="R29" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="S29" s="10">
+        <v>146.70599999999999</v>
+      </c>
+      <c r="T29" s="10">
+        <v>6.1127500000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>23</v>
       </c>
@@ -2021,14 +2834,47 @@
       <c r="G30" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
+      <c r="H30" s="9">
+        <v>70</v>
+      </c>
+      <c r="I30" s="9">
+        <v>166</v>
+      </c>
       <c r="J30" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="K30" s="2"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="9">
+        <v>73</v>
+      </c>
+      <c r="L30" s="10">
+        <v>1.5469999999999999</v>
+      </c>
+      <c r="M30" s="10">
+        <v>1900</v>
+      </c>
+      <c r="N30" s="10">
+        <v>671.75</v>
+      </c>
+      <c r="O30" s="10">
+        <v>2939.4989999999998</v>
+      </c>
+      <c r="P30" s="10">
+        <v>1039.2678000000001</v>
+      </c>
+      <c r="Q30" s="10">
+        <v>439.25700000000001</v>
+      </c>
+      <c r="R30" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="S30" s="10">
+        <v>189.53299999999999</v>
+      </c>
+      <c r="T30" s="10">
+        <v>7.8971989999999996</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>23</v>
       </c>
@@ -2050,14 +2896,47 @@
       <c r="G31" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
+      <c r="H31" s="9">
+        <v>70</v>
+      </c>
+      <c r="I31" s="9">
+        <v>166</v>
+      </c>
       <c r="J31" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="K31" s="2"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="9">
+        <v>73</v>
+      </c>
+      <c r="L31" s="10">
+        <v>1.4379999999999999</v>
+      </c>
+      <c r="M31" s="10">
+        <v>2900</v>
+      </c>
+      <c r="N31" s="10">
+        <v>883.78</v>
+      </c>
+      <c r="O31" s="10">
+        <v>4171.643</v>
+      </c>
+      <c r="P31" s="10">
+        <v>1271.3154999999999</v>
+      </c>
+      <c r="Q31" s="10">
+        <v>878.51400000000001</v>
+      </c>
+      <c r="R31" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="S31" s="10">
+        <v>172.91300000000001</v>
+      </c>
+      <c r="T31" s="10">
+        <v>7.2047210000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>23</v>
       </c>
@@ -2079,16 +2958,47 @@
       <c r="G32" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="H32" s="2"/>
+      <c r="H32" s="9">
+        <v>70</v>
+      </c>
       <c r="I32" s="2" t="s">
         <v>132</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="K32" s="2"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K32" s="9">
+        <v>73</v>
+      </c>
+      <c r="L32" s="10">
+        <v>1.4490000000000001</v>
+      </c>
+      <c r="M32" s="10">
+        <v>4073</v>
+      </c>
+      <c r="N32" s="10">
+        <v>1262.21</v>
+      </c>
+      <c r="O32" s="10">
+        <v>5902.674</v>
+      </c>
+      <c r="P32" s="10">
+        <v>1829.2203</v>
+      </c>
+      <c r="Q32" s="10">
+        <v>2314.8150000000001</v>
+      </c>
+      <c r="R32" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="S32" s="10">
+        <v>182.49600000000001</v>
+      </c>
+      <c r="T32" s="10">
+        <v>7.6039880000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>24</v>
       </c>
@@ -2110,12 +3020,47 @@
       <c r="G33" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H33" s="9">
+        <v>42</v>
+      </c>
+      <c r="I33" s="9">
+        <v>1493</v>
+      </c>
+      <c r="J33" s="9">
+        <v>3</v>
+      </c>
+      <c r="K33" s="9">
+        <v>371</v>
+      </c>
+      <c r="L33" s="10">
+        <v>1.2729999999999999</v>
+      </c>
+      <c r="M33" s="10">
+        <v>93.8</v>
+      </c>
+      <c r="N33" s="10">
+        <v>0.92</v>
+      </c>
+      <c r="O33" s="10">
+        <v>119.396</v>
+      </c>
+      <c r="P33" s="10">
+        <v>1.1711</v>
+      </c>
+      <c r="Q33" s="10">
+        <v>35.164000000000001</v>
+      </c>
+      <c r="R33" s="9">
+        <v>0.08</v>
+      </c>
+      <c r="S33" s="10">
+        <v>37.965000000000003</v>
+      </c>
+      <c r="T33" s="10">
+        <v>1.5818559999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>24</v>
       </c>
@@ -2131,7 +3076,9 @@
       <c r="E34" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="F34" s="2"/>
+      <c r="F34" s="9">
+        <v>1.9</v>
+      </c>
       <c r="G34" s="2" t="s">
         <v>138</v>
       </c>
@@ -2141,12 +3088,41 @@
       <c r="I34" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="J34" s="2"/>
+      <c r="J34" s="9">
+        <v>3</v>
+      </c>
       <c r="K34" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="10">
+        <v>1</v>
+      </c>
+      <c r="M34" s="10">
+        <v>270</v>
+      </c>
+      <c r="N34" s="10">
+        <v>0</v>
+      </c>
+      <c r="O34" s="10">
+        <v>270</v>
+      </c>
+      <c r="P34" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="10">
+        <v>29.509</v>
+      </c>
+      <c r="R34" s="9">
+        <v>0.08</v>
+      </c>
+      <c r="S34" s="10">
+        <v>3.5169999999999999</v>
+      </c>
+      <c r="T34" s="10">
+        <v>0.14654</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>25</v>
       </c>
@@ -2168,16 +3144,47 @@
       <c r="G35" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="H35" s="2"/>
+      <c r="H35" s="9">
+        <v>88</v>
+      </c>
       <c r="I35" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="J35" s="2"/>
+      <c r="J35" s="9">
+        <v>51</v>
+      </c>
       <c r="K35" s="2" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="10">
+        <v>1</v>
+      </c>
+      <c r="M35" s="10">
+        <v>1.9</v>
+      </c>
+      <c r="N35" s="10">
+        <v>0</v>
+      </c>
+      <c r="O35" s="10">
+        <v>1.9</v>
+      </c>
+      <c r="P35" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="10">
+        <v>0.252</v>
+      </c>
+      <c r="R35" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="S35" s="10">
+        <v>8.4979999999999993</v>
+      </c>
+      <c r="T35" s="10">
+        <v>0.35406900000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>26</v>
       </c>
@@ -2187,24 +3194,59 @@
       <c r="C36" s="2">
         <v>4</v>
       </c>
-      <c r="D36" s="2"/>
+      <c r="D36" s="10">
+        <v>1.3754</v>
+      </c>
       <c r="E36" s="2">
         <v>5.5</v>
       </c>
       <c r="F36" s="2">
         <v>4</v>
       </c>
-      <c r="G36" s="2"/>
+      <c r="G36" s="9">
+        <v>10</v>
+      </c>
       <c r="H36" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="I36" s="2"/>
+      <c r="I36" s="9">
+        <v>10</v>
+      </c>
       <c r="J36" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="K36" s="2"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K36" s="9">
+        <v>14.7</v>
+      </c>
+      <c r="L36" s="10">
+        <v>1.234</v>
+      </c>
+      <c r="M36" s="10">
+        <v>5.5</v>
+      </c>
+      <c r="N36" s="10">
+        <v>1.3754</v>
+      </c>
+      <c r="O36" s="10">
+        <v>6.7859999999999996</v>
+      </c>
+      <c r="P36" s="10">
+        <v>1.6970000000000001</v>
+      </c>
+      <c r="Q36" s="10">
+        <v>182.22200000000001</v>
+      </c>
+      <c r="R36" s="9">
+        <v>2.19</v>
+      </c>
+      <c r="S36" s="10">
+        <v>16.32</v>
+      </c>
+      <c r="T36" s="10">
+        <v>0.67998999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>26</v>
       </c>
@@ -2214,22 +3256,57 @@
       <c r="C37" s="2">
         <v>8</v>
       </c>
-      <c r="D37" s="2"/>
+      <c r="D37" s="10">
+        <v>0</v>
+      </c>
       <c r="E37" s="2" t="s">
         <v>149</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
+      <c r="G37" s="9">
+        <v>1</v>
+      </c>
+      <c r="H37" s="9">
+        <v>65</v>
+      </c>
       <c r="I37" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="J37" s="2"/>
+      <c r="J37" s="9">
+        <v>21</v>
+      </c>
       <c r="K37" s="2"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L37" s="10">
+        <v>1</v>
+      </c>
+      <c r="M37" s="10">
+        <v>29</v>
+      </c>
+      <c r="N37" s="10">
+        <v>0</v>
+      </c>
+      <c r="O37" s="10">
+        <v>29</v>
+      </c>
+      <c r="P37" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="10">
+        <v>97.597999999999999</v>
+      </c>
+      <c r="R37" s="9">
+        <v>2.19</v>
+      </c>
+      <c r="S37" s="10">
+        <v>3.7280000000000002</v>
+      </c>
+      <c r="T37" s="10">
+        <v>0.15532699999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>27</v>
       </c>
@@ -2263,8 +3340,35 @@
       <c r="K38" s="2">
         <v>9.5</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="10">
+        <v>1.04</v>
+      </c>
+      <c r="M38" s="10">
+        <v>3000</v>
+      </c>
+      <c r="N38" s="10">
+        <v>114.95</v>
+      </c>
+      <c r="O38" s="10">
+        <v>3119.616</v>
+      </c>
+      <c r="P38" s="10">
+        <v>119.5333</v>
+      </c>
+      <c r="Q38" s="10">
+        <v>105.21899999999999</v>
+      </c>
+      <c r="R38" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="S38" s="10">
+        <v>60.850999999999999</v>
+      </c>
+      <c r="T38" s="10">
+        <v>2.5354679999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>28</v>
       </c>
@@ -2274,14 +3378,18 @@
       <c r="C39" s="2">
         <v>25</v>
       </c>
-      <c r="D39" s="2"/>
+      <c r="D39" s="10">
+        <v>29.861699999999999</v>
+      </c>
       <c r="E39" s="2" t="s">
         <v>153</v>
       </c>
       <c r="F39" s="2">
         <v>1.5</v>
       </c>
-      <c r="G39" s="2"/>
+      <c r="G39" s="9">
+        <v>10</v>
+      </c>
       <c r="H39" s="4">
         <v>0.72</v>
       </c>
@@ -2289,9 +3397,38 @@
         <v>154</v>
       </c>
       <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K39" s="10">
+        <v>287.39999999999998</v>
+      </c>
+      <c r="L39" s="10">
+        <v>1.234</v>
+      </c>
+      <c r="M39" s="10">
+        <v>142</v>
+      </c>
+      <c r="N39" s="10">
+        <v>29.861699999999999</v>
+      </c>
+      <c r="O39" s="10">
+        <v>175.20699999999999</v>
+      </c>
+      <c r="P39" s="10">
+        <v>36.844999999999999</v>
+      </c>
+      <c r="Q39" s="10">
+        <v>37.651000000000003</v>
+      </c>
+      <c r="R39" s="9">
+        <v>5</v>
+      </c>
+      <c r="S39" s="10">
+        <v>51.320999999999998</v>
+      </c>
+      <c r="T39" s="10">
+        <v>2.138366</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>28</v>
       </c>
@@ -2301,14 +3438,18 @@
       <c r="C40" s="2">
         <v>12.5</v>
       </c>
-      <c r="D40" s="2"/>
+      <c r="D40" s="10">
+        <v>14.720599999999999</v>
+      </c>
       <c r="E40" s="2" t="s">
         <v>155</v>
       </c>
       <c r="F40" s="2">
         <v>1.5</v>
       </c>
-      <c r="G40" s="2"/>
+      <c r="G40" s="9">
+        <v>10</v>
+      </c>
       <c r="H40" s="4">
         <v>0.68</v>
       </c>
@@ -2316,9 +3457,38 @@
         <v>156</v>
       </c>
       <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K40" s="10">
+        <v>298.7</v>
+      </c>
+      <c r="L40" s="10">
+        <v>1.234</v>
+      </c>
+      <c r="M40" s="10">
+        <v>70</v>
+      </c>
+      <c r="N40" s="10">
+        <v>14.720599999999999</v>
+      </c>
+      <c r="O40" s="10">
+        <v>86.37</v>
+      </c>
+      <c r="P40" s="10">
+        <v>18.163</v>
+      </c>
+      <c r="Q40" s="10">
+        <v>17.11</v>
+      </c>
+      <c r="R40" s="9">
+        <v>5</v>
+      </c>
+      <c r="S40" s="10">
+        <v>41.113999999999997</v>
+      </c>
+      <c r="T40" s="10">
+        <v>1.713085</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>28</v>
       </c>
@@ -2328,14 +3498,18 @@
       <c r="C41" s="2">
         <v>50</v>
       </c>
-      <c r="D41" s="2"/>
+      <c r="D41" s="10">
+        <v>54.676400000000001</v>
+      </c>
       <c r="E41" s="2" t="s">
         <v>157</v>
       </c>
       <c r="F41" s="2">
         <v>1.5</v>
       </c>
-      <c r="G41" s="2"/>
+      <c r="G41" s="9">
+        <v>10</v>
+      </c>
       <c r="H41" s="4">
         <v>0.65</v>
       </c>
@@ -2343,9 +3517,38 @@
         <v>158</v>
       </c>
       <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K41" s="10">
+        <v>294.39999999999998</v>
+      </c>
+      <c r="L41" s="10">
+        <v>1.234</v>
+      </c>
+      <c r="M41" s="10">
+        <v>260</v>
+      </c>
+      <c r="N41" s="10">
+        <v>54.676400000000001</v>
+      </c>
+      <c r="O41" s="10">
+        <v>320.80200000000002</v>
+      </c>
+      <c r="P41" s="10">
+        <v>67.462699999999998</v>
+      </c>
+      <c r="Q41" s="10">
+        <v>66.381</v>
+      </c>
+      <c r="R41" s="9">
+        <v>5</v>
+      </c>
+      <c r="S41" s="10">
+        <v>60.048999999999999</v>
+      </c>
+      <c r="T41" s="10">
+        <v>2.5020359999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>28</v>
       </c>
@@ -2367,14 +3570,47 @@
       <c r="G42" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
+      <c r="H42" s="9">
+        <v>65</v>
+      </c>
+      <c r="I42" s="9">
+        <v>340</v>
+      </c>
       <c r="J42" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="K42" s="2"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K42" s="10">
+        <v>167.8</v>
+      </c>
+      <c r="L42" s="10">
+        <v>1.0569999999999999</v>
+      </c>
+      <c r="M42" s="10">
+        <v>4573</v>
+      </c>
+      <c r="N42" s="10">
+        <v>247.01</v>
+      </c>
+      <c r="O42" s="10">
+        <v>4834.28</v>
+      </c>
+      <c r="P42" s="10">
+        <v>261.12299999999999</v>
+      </c>
+      <c r="Q42" s="10">
+        <v>106.209</v>
+      </c>
+      <c r="R42" s="9">
+        <v>5</v>
+      </c>
+      <c r="S42" s="10">
+        <v>56.54</v>
+      </c>
+      <c r="T42" s="10">
+        <v>2.3558249999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>29</v>
       </c>
@@ -2384,22 +3620,59 @@
       <c r="C43" s="2">
         <v>20</v>
       </c>
-      <c r="D43" s="2"/>
+      <c r="D43" s="10">
+        <v>11.878500000000001</v>
+      </c>
       <c r="E43" s="2" t="s">
         <v>162</v>
       </c>
       <c r="F43" s="2">
         <v>4</v>
       </c>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
+      <c r="G43" s="9">
+        <v>10</v>
+      </c>
+      <c r="H43" s="9">
+        <v>50</v>
+      </c>
+      <c r="I43" s="10">
+        <v>335</v>
+      </c>
       <c r="J43" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="K43" s="2"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K43" s="10">
+        <v>290</v>
+      </c>
+      <c r="L43" s="10">
+        <v>1.234</v>
+      </c>
+      <c r="M43" s="10">
+        <v>47.5</v>
+      </c>
+      <c r="N43" s="10">
+        <v>11.878500000000001</v>
+      </c>
+      <c r="O43" s="10">
+        <v>58.607999999999997</v>
+      </c>
+      <c r="P43" s="10">
+        <v>14.6563</v>
+      </c>
+      <c r="Q43" s="10">
+        <v>20.73</v>
+      </c>
+      <c r="R43" s="9">
+        <v>4.03</v>
+      </c>
+      <c r="S43" s="10">
+        <v>38.631</v>
+      </c>
+      <c r="T43" s="10">
+        <v>1.6096109999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>167</v>
       </c>
@@ -2421,12 +3694,45 @@
       <c r="G44" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
+      <c r="H44" s="9">
+        <v>65</v>
+      </c>
+      <c r="I44" s="9">
+        <v>485</v>
+      </c>
       <c r="J44" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K44" s="2"/>
+      <c r="K44" s="9">
+        <v>49</v>
+      </c>
+      <c r="L44" s="10">
+        <v>1.0009999999999999</v>
+      </c>
+      <c r="M44" s="10">
+        <v>122</v>
+      </c>
+      <c r="N44" s="10">
+        <v>0.09</v>
+      </c>
+      <c r="O44" s="10">
+        <v>122.08799999999999</v>
+      </c>
+      <c r="P44" s="10">
+        <v>9.01E-2</v>
+      </c>
+      <c r="Q44" s="10">
+        <v>9.3070000000000004</v>
+      </c>
+      <c r="R44" s="9">
+        <v>5</v>
+      </c>
+      <c r="S44" s="10">
+        <v>10.605</v>
+      </c>
+      <c r="T44" s="10">
+        <v>0.44187100000000001</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
